--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jul-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jul-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>689.64</v>
+        <v>695.87</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>36935.71</v>
+        <v>37065.48</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>10587.58</v>
+        <v>10624.78</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9288.200000000001</v>
+        <v>9324.450000000001</v>
       </c>
     </row>
     <row r="6">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>577504.36</v>
+        <v>581414.84</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1636.26</v>
+        <v>1647.34</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7026.3</v>
+        <v>7073.88</v>
       </c>
     </row>
     <row r="9">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>154771.17</v>
+        <v>154472.86</v>
       </c>
     </row>
     <row r="10">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>19346.4</v>
+        <v>19309.11</v>
       </c>
     </row>
     <row r="11">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1184.45</v>
+        <v>1177.97</v>
       </c>
     </row>
     <row r="12">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10491.33</v>
+        <v>10433.97</v>
       </c>
     </row>
     <row r="13">
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1406029.91</v>
+        <v>1399224.97</v>
       </c>
     </row>
     <row r="14">
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7796.31</v>
+        <v>7849.1</v>
       </c>
     </row>
     <row r="15">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>36334.65</v>
+        <v>36580.68</v>
       </c>
     </row>
     <row r="16">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>36890</v>
+        <v>37139.79</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jul-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jul-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -808,7 +808,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jul-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jul-2026.xlsx
@@ -914,7 +914,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jul-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jul-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +887,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +952,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1123,7 +1147,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1184,7 +1212,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1310,7 +1342,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1371,7 +1407,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1432,7 +1472,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jul-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/jul-2026.xlsx
@@ -859,7 +859,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
